--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487170_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487170_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.283</v>
+        <v>2.0419</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8006</v>
+        <v>0.657</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4824</v>
+        <v>1.3848</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0143</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>5.6098</v>
+        <v>2.3686</v>
       </c>
       <c r="T2" t="n">
-        <v>3.543</v>
+        <v>1.3994</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0668</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6985</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.558</v>
+        <v>1.7673</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8244</v>
+        <v>1.3178</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2664</v>
+        <v>0.4495</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6349</v>
+        <v>1.1655</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9623</v>
+        <v>0.9863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6726</v>
+        <v>0.1792</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2828</v>
+        <v>2.6933</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3699</v>
+        <v>1.4073</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9129</v>
+        <v>1.286</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6479</v>
+        <v>-1.5278</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4076</v>
+        <v>-0.421</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2403</v>
+        <v>-1.1067</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0582</v>
+        <v>0.6018</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7998</v>
+        <v>0.5546</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2584</v>
+        <v>0.0472</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5561</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9731</v>
+        <v>1.2765</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6575</v>
+        <v>2.7838</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3157</v>
+        <v>-1.5073</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1655</v>
+        <v>2.6349</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9863</v>
+        <v>1.9623</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1792</v>
+        <v>0.6726</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6933</v>
+        <v>4.2828</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4073</v>
+        <v>2.3699</v>
       </c>
       <c r="L4" t="n">
-        <v>1.286</v>
+        <v>1.9129</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5278</v>
+        <v>-1.6479</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.421</v>
+        <v>-0.4076</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1067</v>
+        <v>-1.2403</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>-0.579</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1924</v>
+        <v>0.7766</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1057</v>
+        <v>0.7592</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0866</v>
+        <v>0.0175</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.5561</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4048</v>
+        <v>1.0185</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3871</v>
+        <v>0.9473</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0177</v>
+        <v>0.0712</v>
       </c>
       <c r="G5" t="n">
         <v>0.6526999999999999</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1719</v>
+        <v>0.4419</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1652</v>
+        <v>0.395</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0066</v>
+        <v>0.0469</v>
       </c>
       <c r="V5" t="n">
         <v>3.398</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2313</v>
+        <v>0.379</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5681</v>
+        <v>0.3678</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3368</v>
+        <v>0.0112</v>
       </c>
       <c r="G6" t="n">
         <v>0.3053</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1117</v>
+        <v>0.2594</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6808</v>
+        <v>0.4806</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.2211</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5717</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2985</v>
+        <v>0.229</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0136</v>
+        <v>0.4871</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2849</v>
+        <v>-0.2581</v>
       </c>
       <c r="G7" t="n">
         <v>0.6372</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0707</v>
+        <v>0.4567</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.119</v>
+        <v>0.3817</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0482</v>
+        <v>0.075</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6203</v>
+        <v>-0.1951</v>
       </c>
       <c r="E8" t="n">
-        <v>1.654</v>
+        <v>2.858</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2743</v>
+        <v>-3.0531</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4215</v>
+        <v>1.8342</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2533</v>
+        <v>1.1944</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8318</v>
+        <v>0.6398</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4623</v>
+        <v>2.7549</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3402</v>
+        <v>1.4282</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>1.3267</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0408</v>
+        <v>-0.9207</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.2338</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9539</v>
+        <v>-0.6869</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.507</v>
+        <v>0.3265</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1917</v>
+        <v>0.1031</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3153</v>
+        <v>0.2234</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1278</v>
+        <v>-2.7418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1278</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7224</v>
+        <v>-0.6956</v>
       </c>
       <c r="E9" t="n">
         <v>0.0207</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7431</v>
+        <v>-0.7163</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7997</v>
@@ -1156,13 +1156,13 @@
         <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8098</v>
+        <v>-0.7938</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4575</v>
+        <v>1.4537</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2673</v>
+        <v>-2.2476</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8342</v>
+        <v>0.4215</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1944</v>
+        <v>1.2533</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6398</v>
+        <v>-0.8318</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7549</v>
+        <v>1.4623</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4282</v>
+        <v>1.3402</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3267</v>
+        <v>0.1221</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9207</v>
+        <v>-1.0408</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2338</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6869</v>
+        <v>-0.9539</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2882</v>
+        <v>0.3335</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2974</v>
+        <v>-0.0086</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0092</v>
+        <v>0.3421</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7418</v>
+        <v>-2.1278</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7418</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0415</v>
+        <v>-1.4069</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.406</v>
+        <v>-1.9053</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3645</v>
+        <v>0.4984</v>
       </c>
       <c r="G11" t="n">
         <v>0.0664</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1778</v>
+        <v>0.4567</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2974</v>
+        <v>0.2033</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1196</v>
+        <v>0.2535</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5496</v>
+        <v>-2.9151</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1712</v>
+        <v>-1.9114</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3785</v>
+        <v>-1.0037</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3558</v>
@@ -1390,13 +1390,13 @@
         <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>0.115</v>
+        <v>0.7496</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1322</v>
+        <v>0.392</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0172</v>
+        <v>0.3576</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1857</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4080999999999992</v>
+        <v>0.7057000000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>6.779099999999999</v>
+        <v>7.076499999999998</v>
       </c>
       <c r="F13" t="n">
         <v>-6.371</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5479</v>
+        <v>6.547899999999998</v>
       </c>
       <c r="H13" t="n">
         <v>7.979399999999999</v>
@@ -1468,13 +1468,13 @@
         <v>11.5805</v>
       </c>
       <c r="S13" t="n">
-        <v>6.385</v>
+        <v>6.682399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.362800000000001</v>
+        <v>4.660299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0223</v>
+        <v>2.0225</v>
       </c>
       <c r="V13" t="n">
         <v>-5.7695</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3872</v>
+        <v>5.0952</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2255</v>
+        <v>3.8263</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1618</v>
+        <v>1.2689</v>
       </c>
       <c r="G14" t="n">
         <v>3.9732</v>
@@ -1546,13 +1546,13 @@
         <v>2.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6511</v>
+        <v>-0.9432</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9518</v>
+        <v>-0.351</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6993</v>
+        <v>-0.5923</v>
       </c>
       <c r="V14" t="n">
         <v>0.3281</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1378</v>
+        <v>4.5384</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1172</v>
+        <v>5.5178</v>
       </c>
       <c r="F15" t="n">
         <v>-0.9794</v>
@@ -1624,10 +1624,10 @@
         <v>3.2811</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3511</v>
+        <v>-0.9505</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7006</v>
+        <v>-0.3001</v>
       </c>
       <c r="U15" t="n">
         <v>-0.6504</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0754</v>
+        <v>3.8215</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8022</v>
+        <v>2.6019</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2731</v>
+        <v>1.2196</v>
       </c>
       <c r="G16" t="n">
         <v>1.9003</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2882</v>
+        <v>-0.542</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2512</v>
+        <v>0.0509</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5394</v>
+        <v>-0.5929</v>
       </c>
       <c r="V16" t="n">
         <v>1.8842</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3875</v>
+        <v>0.7912</v>
       </c>
       <c r="E17" t="n">
-        <v>2.307</v>
+        <v>1.0052</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0805</v>
+        <v>-0.214</v>
       </c>
       <c r="G17" t="n">
         <v>-3.5277</v>
@@ -1780,13 +1780,13 @@
         <v>2.8951</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4363</v>
+        <v>-0.16</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4212</v>
+        <v>0.1193</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0152</v>
+        <v>-0.2793</v>
       </c>
       <c r="V17" t="n">
         <v>2.7418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4757</v>
+        <v>0.1555</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1446</v>
+        <v>0.744</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.5886</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0524</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1421</v>
+        <v>-0.1781</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4891</v>
+        <v>0.0886</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5942</v>
+        <v>-0.0528</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6708</v>
+        <v>1.9713</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.265</v>
+        <v>-2.0241</v>
       </c>
       <c r="G19" t="n">
         <v>0.0027</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3689</v>
+        <v>-0.8276</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6544</v>
+        <v>-0.3539</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7145</v>
+        <v>-0.4736</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7675</v>
+        <v>-3.0412</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.434</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3336</v>
+        <v>-2.3068</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5068</v>
@@ -2014,13 +2014,13 @@
         <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5321</v>
+        <v>-0.8057</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.033</v>
+        <v>-0.3334</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4991</v>
+        <v>-0.4723</v>
       </c>
       <c r="V20" t="n">
         <v>0.8154</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8627</v>
+        <v>-5.2153</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1364</v>
+        <v>-4.4354</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7264</v>
+        <v>-0.7799</v>
       </c>
       <c r="G21" t="n">
         <v>-5.8574</v>
@@ -2092,13 +2092,13 @@
         <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5494</v>
+        <v>-0.9019</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1303</v>
+        <v>-0.4293</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4191</v>
+        <v>-0.4726</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6473</v>
+        <v>-6.5006</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.326</v>
+        <v>-4.1257</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3213</v>
+        <v>-2.3749</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1037</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2228</v>
+        <v>-1.0761</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7139</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.509</v>
+        <v>-0.5625</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4081000000000001</v>
+        <v>-0.4080999999999975</v>
       </c>
       <c r="E23" t="n">
-        <v>6.3709</v>
+        <v>6.371</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.7792</v>
+        <v>-6.779199999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-6.5478</v>
@@ -2248,7 +2248,7 @@
         <v>18.3357</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.3852</v>
+        <v>-6.3851</v>
       </c>
       <c r="T23" t="n">
         <v>-2.0225</v>
